--- a/data/trans_orig/IP2902-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34747</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46003</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65581</t>
+          <t>65418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>17447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>59963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37449</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52502</t>
+          <t>52066</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86919</t>
+          <t>87338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107865</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80805</t>
+          <t>80260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108027</t>
+          <t>107423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101594</t>
+          <t>103651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132975</t>
+          <t>133149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191407</t>
+          <t>191043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>232633</t>
+          <t>231311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35357</t>
+          <t>35632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55949</t>
+          <t>56880</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44593</t>
+          <t>45315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67699</t>
+          <t>68647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87478</t>
+          <t>87793</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>117624</t>
+          <t>118380</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>250085</t>
+          <t>249934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280127</t>
+          <t>280768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>270971</t>
+          <t>270834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>305783</t>
+          <t>304516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>528716</t>
+          <t>529362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>575237</t>
+          <t>575910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30577</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57003</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80618</t>
+          <t>81133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30369</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31868</t>
+          <t>33084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>37243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58301</t>
+          <t>57289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94781</t>
+          <t>94822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116117</t>
+          <t>114122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90833</t>
+          <t>89793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109328</t>
+          <t>109314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190394</t>
+          <t>192466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217601</t>
+          <t>219973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>142679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177498</t>
+          <t>177534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157390</t>
+          <t>154856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192759</t>
+          <t>190936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>308904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362492</t>
+          <t>361150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90879</t>
+          <t>93239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79424</t>
+          <t>76751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106962</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151663</t>
+          <t>152631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190187</t>
+          <t>191101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>401969</t>
+          <t>403199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>442491</t>
+          <t>440745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>410568</t>
+          <t>412459</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>450919</t>
+          <t>453417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>825375</t>
+          <t>828218</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>882190</t>
+          <t>883302</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35317</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>35117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>65349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>31057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57395</t>
+          <t>57512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39842</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54470</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84870</t>
+          <t>86515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108220</t>
+          <t>107008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116103</t>
+          <t>116807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149290</t>
+          <t>147924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144094</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>177734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269141</t>
+          <t>269632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315587</t>
+          <t>315441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>42269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64254</t>
+          <t>64981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40565</t>
+          <t>41423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89065</t>
+          <t>87312</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119387</t>
+          <t>119921</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246825</t>
+          <t>246206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>281613</t>
+          <t>281121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257002</t>
+          <t>257769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>294358</t>
+          <t>295833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>517103</t>
+          <t>512780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566709</t>
+          <t>566163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51533</t>
+          <t>51950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>57177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75520</t>
+          <t>75518</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>102501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>21099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>22191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57833</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96232</t>
+          <t>96311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116046</t>
+          <t>116283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77715</t>
+          <t>78595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98509</t>
+          <t>100335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179519</t>
+          <t>180614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208475</t>
+          <t>209084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>183510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219449</t>
+          <t>222753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>213133</t>
+          <t>213325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257448</t>
+          <t>254442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>407417</t>
+          <t>407286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>464033</t>
+          <t>465076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>68087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76923</t>
+          <t>77304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106304</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152458</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194953</t>
+          <t>192541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>398306</t>
+          <t>398049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440979</t>
+          <t>441660</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>390115</t>
+          <t>391375</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>435809</t>
+          <t>435541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>803843</t>
+          <t>800909</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>860533</t>
+          <t>861504</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>32922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>33527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>50585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76084</t>
+          <t>75722</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93554</t>
+          <t>93250</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89142</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117378</t>
+          <t>117193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82589</t>
+          <t>82702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112067</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179431</t>
+          <t>178490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219691</t>
+          <t>220795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58254</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84248</t>
+          <t>84267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62819</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89420</t>
+          <t>88754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>129913</t>
+          <t>128374</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165721</t>
+          <t>165476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271786</t>
+          <t>271517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303855</t>
+          <t>305297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287076</t>
+          <t>286026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>320433</t>
+          <t>321848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565816</t>
+          <t>567799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>615330</t>
+          <t>615081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64519</t>
+          <t>63537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41123</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50878</t>
+          <t>49992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73390</t>
+          <t>73921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105755</t>
+          <t>106265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126187</t>
+          <t>125876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110790</t>
+          <t>110508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131288</t>
+          <t>132837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222177</t>
+          <t>224465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251501</t>
+          <t>254301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>121796</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156203</t>
+          <t>155373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121927</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>155888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253969</t>
+          <t>254897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299064</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>92687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>124248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132128</t>
+          <t>132961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>200036</t>
+          <t>202845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>244968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>422892</t>
+          <t>423121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>463413</t>
+          <t>463199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>447788</t>
+          <t>451236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>490310</t>
+          <t>490771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>883189</t>
+          <t>886026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>940397</t>
+          <t>944300</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2902-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>27708</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21118</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34636</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>27390</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20710</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35396</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21362</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27708</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21033</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>34629</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46237</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65418</t>
+          <t>64417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17637</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9305</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5613</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14794</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5237</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11612</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17447</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28198</t>
+          <t>29315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>44816</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36463</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51571</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>53,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>43,34%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52744</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45136</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>59963</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>43990</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>59735</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>58,97%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>50,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>44816</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37810</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>52066</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>53,27%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87338</t>
+          <t>87249</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107672</t>
+          <t>107459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89438</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>89438</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>89438</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>117239</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100924</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131027</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>94032</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80260</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>107423</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80123</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>106914</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>117239</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103651</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>133149</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>25,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191043</t>
+          <t>190136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231311</t>
+          <t>233716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45212</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67297</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45912</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35632</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>56880</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>36684</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>56181</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,36%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>56418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45315</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>68647</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87793</t>
+          <t>86705</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118380</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>287384</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>271480</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>303629</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>398</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>264358</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>249934</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>280768</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>248664</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>279133</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>65,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>287384</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>270834</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>304516</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>529362</t>
+          <t>528429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>575910</t>
+          <t>575569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>461041</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>461041</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>461041</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>611</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>404303</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>404303</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>404303</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>461041</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>461041</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>461041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29337</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21678</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38513</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>25,11%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38769</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31087</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48821</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>30006</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>48117</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>23,18%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29337</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21991</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37726</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56808</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81133</t>
+          <t>80936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24105</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18099</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32389</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>23100</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16902</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30832</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15988</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30184</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24105</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17406</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33084</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37243</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57289</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>99951</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90236</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>109748</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>105387</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>94822</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>114122</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95914</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>115320</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>99951</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89793</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>109314</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,16%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192466</t>
+          <t>191091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219973</t>
+          <t>219530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>153392</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>153392</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>153392</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167256</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167256</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167256</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>153392</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>153392</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>153392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>174283</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>158000</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>193958</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>160191</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>142679</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>177534</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>143238</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>178116</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>24,23%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>174283</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>154856</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>190936</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308904</t>
+          <t>310938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361150</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>92135</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78419</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>106756</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>78317</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>66446</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93239</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>65561</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>92243</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>76751</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>106257</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152631</t>
+          <t>151523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191101</t>
+          <t>193448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>432150</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>411508</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>451955</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>61,86%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>64,7%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>422489</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>403199</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>440745</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>402912</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>442704</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>63,92%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>432150</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>412459</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>828218</t>
+          <t>823340</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>883302</t>
+          <t>881373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>698568</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>698568</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>698568</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>660997</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>660997</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>660997</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>698568</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>698568</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>698568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2777,72 +2777,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27646</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20999</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35027</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20333</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35732</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20933</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35299</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27646</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21256</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35117</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65349</t>
+          <t>65654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -2890,72 +2890,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14814</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13663</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9311</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20527</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8354</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20229</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31057</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -3003,72 +3003,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47354</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39790</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54900</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>56,61%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>47,57%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>65,63%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>49696</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41527</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57512</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>42488</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>57818</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>54,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>45,63%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>63,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>47354</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39387</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>54091</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>56,61%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86515</t>
+          <t>86093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107008</t>
+          <t>107842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3233,72 +3233,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>159220</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>143573</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>175449</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>131938</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>116807</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>147924</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>116017</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>148483</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>159220</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>142747</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>177734</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269632</t>
+          <t>267673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315441</t>
+          <t>314287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -3346,72 +3346,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50959</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41192</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>63227</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52797</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>42269</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>64981</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>42120</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>64607</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50959</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41423</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>62891</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87312</t>
+          <t>88389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119921</t>
+          <t>121388</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>276822</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>257881</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>293826</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>380</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>263977</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>246206</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>281121</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>246314</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>282012</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>58,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>276822</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>257769</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>295833</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>512780</t>
+          <t>514107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566163</t>
+          <t>564513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -3572,57 +3572,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>487000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>487000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>487000</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>448712</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>448712</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>448712</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>487000</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>487000</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>487000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3689,72 +3689,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>46946</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38402</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56782</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>41975</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33868</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51950</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>33043</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>52503</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>25,81%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>46946</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37023</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>57177</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75518</t>
+          <t>76689</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102501</t>
+          <t>102663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -3802,72 +3802,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31910</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24333</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40607</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>14564</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8979</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21099</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9537</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21442</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>31910</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22191</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>40068</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>57504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -3915,72 +3915,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89002</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78388</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99601</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>106102</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>96311</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116283</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95547</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>116745</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>89002</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>100335</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>53,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180614</t>
+          <t>179805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209084</t>
+          <t>208954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -4028,57 +4028,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167858</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167858</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167858</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162641</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162641</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162641</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167858</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167858</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167858</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>233811</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214617</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>255794</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>201554</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>183510</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>222753</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>182794</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>222607</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>233811</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>213325</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>254442</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>407286</t>
+          <t>406735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>465076</t>
+          <t>462202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -4258,72 +4258,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>91520</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>77086</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>107090</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>81025</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>68087</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>95181</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>68415</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>95817</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>91520</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>77304</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>106107</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152429</t>
+          <t>154040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>192541</t>
+          <t>192935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -4371,72 +4371,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>413178</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>390650</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>434986</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>55,95%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>58,9%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>419776</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>398049</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>441660</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>395958</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>440843</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>59,77%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>56,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>413178</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>391375</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>435541</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>800909</t>
+          <t>803808</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>861504</t>
+          <t>864250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -4484,57 +4484,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>738509</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>738509</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>738509</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>702355</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>702355</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>702355</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>738509</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>738509</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>738509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4832,72 +4832,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20677</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10677</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16147</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6572</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16749</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14217</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9529</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20540</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -4950,67 +4950,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4536</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13407</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>7455</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3890</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12108</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3952</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12245</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,83%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8036</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12497</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22663</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>44840</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37663</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50582</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>66,83%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>56,14%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>75,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>39970</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33527</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>33513</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45088</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>68,79%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>57,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>77,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>44840</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37921</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50585</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75722</t>
+          <t>75403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93250</t>
+          <t>92840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -5171,57 +5171,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58102</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58102</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58102</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5288,72 +5288,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96517</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82677</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110414</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103051</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88174</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>117193</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89298</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>118698</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96517</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82702</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112610</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178490</t>
+          <t>180695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220795</t>
+          <t>221530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -5401,72 +5401,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>75339</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>63742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91973</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15,85%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>19,35%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>70920</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>59000</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>58816</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>84724</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>15,36%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>75339</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>61905</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>88754</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128374</t>
+          <t>128368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165476</t>
+          <t>163856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -5514,72 +5514,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>303457</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>283981</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>319962</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>435</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>287683</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>271517</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>305297</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>270889</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>304429</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>303457</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>286026</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>321848</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>567799</t>
+          <t>566996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>615081</t>
+          <t>616787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -5627,57 +5627,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475314</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475314</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475314</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>698</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>461653</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>461653</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>461653</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>475314</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>475314</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>475314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5744,72 +5744,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27614</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20329</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35957</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,79%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>24136</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17582</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>32631</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17376</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>32890</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>14,25%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27614</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20235</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>36332</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63537</t>
+          <t>63833</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -5857,72 +5857,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32372</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24899</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41752</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29173</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21656</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37386</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22517</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38403</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32372</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23700</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>42027</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49992</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73921</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -5970,72 +5970,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>121699</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>110363</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>131901</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>116067</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106265</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>125876</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>105227</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>125575</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>121699</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>110508</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>132837</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224465</t>
+          <t>223608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254301</t>
+          <t>252134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -6083,57 +6083,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>181685</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181685</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181685</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169375</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169375</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169375</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>181685</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>181685</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>181685</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6200,72 +6200,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>138348</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>121697</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>154568</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>137863</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>121123</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>155373</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>122026</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>154970</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>138348</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>121841</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>155888</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254897</t>
+          <t>253057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300948</t>
+          <t>299968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -6313,72 +6313,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>115748</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101726</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>132174</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>107548</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>92687</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>94122</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>125240</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>15,61%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>115748</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>99988</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>132961</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202845</t>
+          <t>203689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244968</t>
+          <t>245852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -6426,72 +6426,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>469996</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>448422</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>489988</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>64,91%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>61,93%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>67,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>443719</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>423121</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>463199</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>421422</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>461865</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>64,39%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>469996</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>451236</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>490771</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>886026</t>
+          <t>887016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>944300</t>
+          <t>944614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -6539,57 +6539,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>689130</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>689130</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>689130</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
